--- a/Assets/@Resources/Data/Excel/ForgeRecipeData.xlsx
+++ b/Assets/@Resources/Data/Excel/ForgeRecipeData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2440,6 +2441,70 @@
         <v>21</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>40060</v>
+      </c>
+      <c r="B64" t="n">
+        <v>30061</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>90</v>
+      </c>
+      <c r="E64" t="n">
+        <v>11001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>10001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10002</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>40061</v>
+      </c>
+      <c r="B65" t="n">
+        <v>30062</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>90</v>
+      </c>
+      <c r="E65" t="n">
+        <v>11001</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>10002</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>11004</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
